--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42271092-CB2A-4042-8C53-C7291EF6341B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13192AF8-4F1D-4A28-90A3-40138EBE64D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t xml:space="preserve">Enemy </t>
   </si>
@@ -214,6 +214,21 @@
   </si>
   <si>
     <t>20 / 60</t>
+  </si>
+  <si>
+    <t>Item drop</t>
+  </si>
+  <si>
+    <t>Armour plate (15)</t>
+  </si>
+  <si>
+    <t>Suicide Bomber</t>
+  </si>
+  <si>
+    <t>RGD-5</t>
+  </si>
+  <si>
+    <t>grenade</t>
   </si>
 </sst>
 </file>
@@ -618,7 +633,7 @@
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
     <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="15" width="15.59765625" customWidth="1"/>
+    <col min="3" max="16" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -664,7 +679,9 @@
       <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="1"/>
+      <c r="P3" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
@@ -799,24 +816,56 @@
       <c r="O6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="B7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B8" s="5"/>
@@ -859,7 +908,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:Q10"/>
+  <dimension ref="B3:Q11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -1279,6 +1328,56 @@
         <v>0.9</v>
       </c>
     </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>80</v>
+      </c>
+      <c r="G11" s="3">
+        <v>75</v>
+      </c>
+      <c r="H11" s="3">
+        <v>50</v>
+      </c>
+      <c r="I11" s="3">
+        <v>30</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>30</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13192AF8-4F1D-4A28-90A3-40138EBE64D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E407A60-C6F6-42D3-8F77-F6076AD23868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -908,15 +908,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:Q11"/>
+  <dimension ref="B3:R11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
     <col min="2" max="14" width="15.59765625" customWidth="1"/>
     <col min="15" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
@@ -964,6 +965,11 @@
       </c>
       <c r="Q3" s="1" t="s">
         <v>32</v>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>Scope magnification (empty = iron sights)</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
@@ -1224,7 +1230,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -1274,6 +1280,9 @@
       </c>
       <c r="Q9" s="3">
         <v>0.6</v>
+      </c>
+      <c r="R9" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E407A60-C6F6-42D3-8F77-F6076AD23868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F950F4-A748-4C6E-AD07-D8FEDF3FFBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10605" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="70">
   <si>
     <t xml:space="preserve">Enemy </t>
   </si>
@@ -84,9 +84,6 @@
     <t>10 / 30</t>
   </si>
   <si>
-    <t>AK-47, RPG-7</t>
-  </si>
-  <si>
     <t>Weapon</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>Heavy Insurgent</t>
   </si>
   <si>
-    <t>AK-47, RPK</t>
-  </si>
-  <si>
     <t>3 / 7</t>
   </si>
   <si>
@@ -219,9 +213,6 @@
     <t>Item drop</t>
   </si>
   <si>
-    <t>Armour plate (15)</t>
-  </si>
-  <si>
     <t>Suicide Bomber</t>
   </si>
   <si>
@@ -229,6 +220,30 @@
   </si>
   <si>
     <t>grenade</t>
+  </si>
+  <si>
+    <t>Scope magnification (empty = iron sights)</t>
+  </si>
+  <si>
+    <t>FAL</t>
+  </si>
+  <si>
+    <t>Mini Uzi</t>
+  </si>
+  <si>
+    <t>Galil</t>
+  </si>
+  <si>
+    <t>Galil, RPK</t>
+  </si>
+  <si>
+    <t>AK-47, FAL, RPG-7</t>
+  </si>
+  <si>
+    <t>AK-47, Mini Uzi</t>
+  </si>
+  <si>
+    <t>Armour plate (30)</t>
   </si>
 </sst>
 </file>
@@ -644,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
@@ -680,12 +695,12 @@
         <v>12</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3">
         <v>100</v>
@@ -694,43 +709,43 @@
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M4" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3">
         <v>100</v>
@@ -739,13 +754,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F5" s="3">
         <v>30</v>
       </c>
       <c r="G5" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3">
         <v>1.5</v>
@@ -757,25 +772,25 @@
         <v>3</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M5" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3">
         <v>100</v>
@@ -787,7 +802,7 @@
         <v>2.5</v>
       </c>
       <c r="F6" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3">
         <v>35</v>
@@ -796,33 +811,33 @@
         <v>1</v>
       </c>
       <c r="I6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3">
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M6" s="3">
         <v>20</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B7" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3">
         <v>100</v>
@@ -837,34 +852,34 @@
         <v>30</v>
       </c>
       <c r="G7" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3">
         <v>0.5</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" s="3">
         <v>1</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.45">
@@ -908,7 +923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:R11"/>
+  <dimension ref="B3:R18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -919,72 +934,70 @@
   <sheetData>
     <row r="3" spans="2:18" ht="57" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>Scope magnification (empty = iron sights)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C4" s="3">
         <v>17</v>
       </c>
       <c r="D4" s="3">
-        <f>+C4*6</f>
-        <v>102</v>
+        <f>+C4*5</f>
+        <v>85</v>
       </c>
       <c r="E4" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="3">
         <v>20</v>
@@ -999,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K4" s="3">
         <v>180</v>
@@ -1015,286 +1028,291 @@
         <v>187</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="Q4" s="3">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="3">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3">
+        <f>+C5*10</f>
+        <v>200</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3">
-        <v>30</v>
-      </c>
-      <c r="D5" s="3">
-        <f>+C5*8</f>
-        <v>240</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3">
-        <v>35</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="K5" s="3">
-        <v>700</v>
+        <v>950</v>
       </c>
       <c r="L5" s="3">
         <v>25</v>
       </c>
       <c r="M5" s="3">
+        <v>30</v>
+      </c>
+      <c r="N5" s="3">
+        <f>400/2</f>
+        <v>200</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3">
+        <f>+C6*10</f>
+        <v>300</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
         <v>20</v>
       </c>
-      <c r="N5" s="3">
+      <c r="G6" s="3">
+        <v>20</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3">
+        <v>800</v>
+      </c>
+      <c r="L6" s="3">
+        <v>15</v>
+      </c>
+      <c r="M6" s="3">
+        <v>20</v>
+      </c>
+      <c r="N6" s="3">
+        <f>400/2</f>
+        <v>200</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3">
+        <f>+C7*8</f>
+        <v>240</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>35</v>
+      </c>
+      <c r="G7" s="3">
+        <v>35</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="3">
+        <v>700</v>
+      </c>
+      <c r="L7" s="3">
+        <v>25</v>
+      </c>
+      <c r="M7" s="3">
+        <v>20</v>
+      </c>
+      <c r="N7" s="3">
         <f>910/2</f>
         <v>455</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3">
+        <f>+C8*8</f>
+        <v>240</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3">
+        <v>35</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="3">
+        <v>650</v>
+      </c>
+      <c r="L8" s="3">
+        <v>30</v>
+      </c>
+      <c r="M8" s="3">
+        <v>20</v>
+      </c>
+      <c r="N8" s="3">
+        <f>900/2</f>
+        <v>450</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
+      <c r="C9" s="3">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3">
+        <f>+C9*6</f>
+        <v>180</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>40</v>
       </c>
-      <c r="C6" s="3">
+      <c r="G9" s="3">
+        <v>50</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="3">
+        <v>600</v>
+      </c>
+      <c r="L9" s="3">
         <v>30</v>
       </c>
-      <c r="D6" s="3">
-        <f>+C6*6</f>
-        <v>180</v>
-      </c>
-      <c r="E6" s="3">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3">
-        <v>50</v>
-      </c>
-      <c r="H6" s="3">
-        <v>10</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="3">
-        <v>600</v>
-      </c>
-      <c r="L6" s="3">
-        <v>30</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="M9" s="3">
         <v>25</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N9" s="3">
         <f>712/2</f>
         <v>356</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="3">
+      <c r="O9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="3">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3">
-        <v>80</v>
-      </c>
-      <c r="G7" s="3">
-        <v>100</v>
-      </c>
-      <c r="H7" s="3">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3">
-        <v>50</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="3">
-        <v>30</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <v>115</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="3">
-        <v>30</v>
-      </c>
-      <c r="D8" s="3">
-        <f>+C8*10</f>
-        <v>300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>20</v>
-      </c>
-      <c r="G8" s="3">
-        <v>20</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="3">
-        <v>800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>15</v>
-      </c>
-      <c r="M8" s="3">
-        <v>20</v>
-      </c>
-      <c r="N8" s="3">
-        <f>400/2</f>
-        <v>200</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3">
-        <v>10</v>
-      </c>
-      <c r="D9" s="3">
-        <f>+C9*6</f>
-        <v>60</v>
-      </c>
-      <c r="E9" s="3">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3">
-        <v>50</v>
-      </c>
-      <c r="G9" s="3">
-        <v>50</v>
-      </c>
-      <c r="H9" s="3">
-        <v>15</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="3">
-        <v>700</v>
-      </c>
-      <c r="L9" s="3">
-        <v>35</v>
-      </c>
-      <c r="M9" s="3">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3">
-        <f>853/2</f>
-        <v>426.5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="R9" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3">
         <v>75</v>
       </c>
       <c r="D10" s="3">
-        <f>+C10*4</f>
-        <v>300</v>
+        <f>+C10*3</f>
+        <v>225</v>
       </c>
       <c r="E10" s="3">
         <v>6</v>
@@ -1312,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10" s="3">
         <v>600</v>
@@ -1328,64 +1346,301 @@
         <v>372.5</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q10" s="3">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3">
+        <f>+C11*8</f>
+        <v>160</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="3">
+        <v>650</v>
+      </c>
+      <c r="L11" s="3">
+        <v>35</v>
+      </c>
+      <c r="M11" s="3">
+        <v>20</v>
+      </c>
+      <c r="N11" s="3">
+        <f>840/2</f>
+        <v>420</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3">
+        <f>+C12*6</f>
+        <v>60</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3">
+        <v>50</v>
+      </c>
+      <c r="G12" s="3">
+        <v>50</v>
+      </c>
+      <c r="H12" s="3">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="3">
+        <v>700</v>
+      </c>
+      <c r="L12" s="3">
+        <v>35</v>
+      </c>
+      <c r="M12" s="3">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
+        <f>853/2</f>
+        <v>426.5</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="R12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D13" s="3">
         <v>5</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E13" s="3">
         <v>0.1</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F13" s="3">
         <v>80</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G13" s="3">
         <v>75</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H13" s="3">
         <v>50</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I13" s="3">
         <v>30</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="J13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>15</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>80</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>50</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="3">
+        <v>30</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>115</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>15</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="P14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F950F4-A748-4C6E-AD07-D8FEDF3FFBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58427AE-F95A-4F15-8234-002A3C49F5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10605" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -1478,16 +1478,16 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3">
         <v>50</v>
       </c>
       <c r="I13" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>33</v>
@@ -1529,16 +1529,16 @@
         <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
       </c>
       <c r="I14" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>33</v>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -1481,7 +1481,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H13" s="3">
         <v>50</v>
@@ -1532,7 +1532,7 @@
         <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
     <sheet name="Weapons" sheetId="2" r:id="rId2"/>
+    <sheet name="Allies" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1567,22 +1568,56 @@
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Turret</t>
+        </is>
+      </c>
+      <c r="C15" s="3">
+        <v>100</v>
+      </c>
+      <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3">
+        <v>20</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>455</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -1645,4 +1680,123 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0002-000000000000}">
+  <dimension ref="B3:P4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="15.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:16" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Ally</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Turret</t>
+        </is>
+      </c>
+      <c r="C4" s="3">
+        <v>100</v>
+      </c>
+      <c r="D4" s="3">
+        <v>300</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>5 / 10</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>0.5 / 1</t>
+        </is>
+      </c>
+      <c r="M4" s="3">
+        <v>25</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Turret</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58427AE-F95A-4F15-8234-002A3C49F5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D3D8B6-7709-4C9A-A0CE-860B17BDC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
     <sheet name="Weapons" sheetId="2" r:id="rId2"/>
-    <sheet name="Allies" sheetId="3" r:id="rId7"/>
+    <sheet name="Allies" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
   <si>
     <t xml:space="preserve">Enemy </t>
   </si>
@@ -245,6 +245,51 @@
   </si>
   <si>
     <t>Armour plate (30)</t>
+  </si>
+  <si>
+    <t>Turret</t>
+  </si>
+  <si>
+    <t>Ally</t>
+  </si>
+  <si>
+    <t>5 / 10</t>
+  </si>
+  <si>
+    <t>0.5 / 1</t>
+  </si>
+  <si>
+    <t>Machete</t>
+  </si>
+  <si>
+    <t>AK-47, Galil, FAL</t>
+  </si>
+  <si>
+    <t>10 / 20</t>
+  </si>
+  <si>
+    <t>Khat Addict</t>
+  </si>
+  <si>
+    <t>Khat Berserker</t>
+  </si>
+  <si>
+    <t>Kambala Militant</t>
+  </si>
+  <si>
+    <t>0.3 / 1</t>
+  </si>
+  <si>
+    <t>Mini-Uzi</t>
+  </si>
+  <si>
+    <t>Kambala Mercenary</t>
+  </si>
+  <si>
+    <t>4 / 8</t>
+  </si>
+  <si>
+    <t>AK-47, Galil, FAL, RPK</t>
   </si>
 </sst>
 </file>
@@ -644,11 +689,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:P9"/>
+  <dimension ref="B3:P12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.86328125" customWidth="1"/>
     <col min="3" max="16" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -884,38 +929,203 @@
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="3"/>
+      <c r="B8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="3">
+        <v>100</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3">
+        <v>30</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="3">
+        <v>10</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="3"/>
+      <c r="B9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3">
+        <v>100</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" s="3">
+        <v>10</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="3">
+        <v>100</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>25</v>
+      </c>
+      <c r="G10" s="3">
+        <v>25</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="3">
+        <v>100</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3">
+        <v>35</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="3">
+        <v>20</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B12" s="5"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1568,10 +1778,8 @@
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Turret</t>
-        </is>
+      <c r="B15" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C15" s="3">
         <v>100</v>
@@ -1621,22 +1829,54 @@
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
+      <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3">
+        <v>40</v>
+      </c>
+      <c r="G16" s="3">
+        <v>50</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -1693,10 +1933,8 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Ally</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -1742,10 +1980,8 @@
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Turret</t>
-        </is>
+      <c r="B4" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="C4" s="3">
         <v>100</v>
@@ -1771,15 +2007,11 @@
       <c r="J4" s="3">
         <v>2</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>5 / 10</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>0.5 / 1</t>
-        </is>
+      <c r="K4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="M4" s="3">
         <v>25</v>
@@ -1787,10 +2019,8 @@
       <c r="N4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Turret</t>
-        </is>
+      <c r="O4" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>42</v>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -1071,7 +1071,7 @@
         <v>100</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3">
         <v>4</v>
@@ -1871,8 +1871,10 @@
       <c r="O16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>42</v>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
       </c>
       <c r="Q16" s="3" t="s">
         <v>42</v>

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -1882,22 +1882,58 @@
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mortar</t>
+        </is>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>50</v>
+      </c>
+      <c r="H17" s="3">
+        <v>50</v>
+      </c>
+      <c r="I17" s="3">
+        <v>40</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>15</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>mortar</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">

--- a/data/Game Data.xlsx
+++ b/data/Game Data.xlsx
@@ -1937,22 +1937,60 @@
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B18" s="2"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Gunship gun</t>
+        </is>
+      </c>
+      <c r="C18" s="3">
+        <v>600</v>
+      </c>
+      <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>50</v>
+      </c>
+      <c r="G18" s="3">
+        <v>50</v>
+      </c>
+      <c r="H18" s="3">
+        <v>15</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
+      <c r="K18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
+        <v>420</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="R18" s="3"/>
     </row>
   </sheetData>
